--- a/jogos_2025-05-01.xlsx
+++ b/jogos_2025-05-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="211">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -283,12 +229,12 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -328,36 +274,36 @@
     <t>Royal Antwerp FC</t>
   </si>
   <si>
+    <t>Shandong Luneng</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Shandong Luneng</t>
-  </si>
-  <si>
     <t>Bali United</t>
   </si>
   <si>
+    <t>Palermo</t>
+  </si>
+  <si>
+    <t>Spezia</t>
+  </si>
+  <si>
     <t>Sampdoria</t>
   </si>
   <si>
+    <t>Modena</t>
+  </si>
+  <si>
+    <t>Mantova</t>
+  </si>
+  <si>
+    <t>Cosenza</t>
+  </si>
+  <si>
     <t>Pisa</t>
   </si>
   <si>
-    <t>Modena</t>
-  </si>
-  <si>
-    <t>Spezia</t>
-  </si>
-  <si>
-    <t>Palermo</t>
-  </si>
-  <si>
-    <t>Cosenza</t>
-  </si>
-  <si>
-    <t>Mantova</t>
-  </si>
-  <si>
     <t>Ceramica Cleopatra</t>
   </si>
   <si>
@@ -373,39 +319,39 @@
     <t>Cittadella</t>
   </si>
   <si>
+    <t>Chadormalu SC</t>
+  </si>
+  <si>
+    <t>Nassaji Mazandaran</t>
+  </si>
+  <si>
     <t>Mes Rafsanjan</t>
   </si>
   <si>
-    <t>Nassaji Mazandaran</t>
-  </si>
-  <si>
-    <t>Chadormalu SC</t>
+    <t>Esteghlal Khuzestan</t>
+  </si>
+  <si>
+    <t>Al Riyadh</t>
   </si>
   <si>
     <t>Al Akhdoud</t>
   </si>
   <si>
-    <t>Al Riyadh</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Esteghlal Khuzestan</t>
+    <t>Hebar 1918</t>
   </si>
   <si>
     <t>KÍ</t>
   </si>
   <si>
-    <t>Hebar 1918</t>
+    <t>Aqaba</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Aqaba</t>
-  </si>
-  <si>
     <t>Al Masry</t>
   </si>
   <si>
@@ -445,36 +391,36 @@
     <t>RSC Anderlecht</t>
   </si>
   <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
     <t>PSIS Semarang</t>
   </si>
   <si>
+    <t>Südtirol</t>
+  </si>
+  <si>
+    <t>Salernitana</t>
+  </si>
+  <si>
     <t>Cremonese</t>
   </si>
   <si>
+    <t>Reggiana</t>
+  </si>
+  <si>
+    <t>Cesena</t>
+  </si>
+  <si>
+    <t>Bari 1908</t>
+  </si>
+  <si>
     <t>Frosinone</t>
   </si>
   <si>
-    <t>Reggiana</t>
-  </si>
-  <si>
-    <t>Salernitana</t>
-  </si>
-  <si>
-    <t>Südtirol</t>
-  </si>
-  <si>
-    <t>Bari 1908</t>
-  </si>
-  <si>
-    <t>Cesena</t>
-  </si>
-  <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
@@ -490,39 +436,39 @@
     <t>Brescia</t>
   </si>
   <si>
+    <t>Foolad</t>
+  </si>
+  <si>
+    <t>Havadar</t>
+  </si>
+  <si>
     <t>Persepolis</t>
   </si>
   <si>
-    <t>Havadar</t>
-  </si>
-  <si>
-    <t>Foolad</t>
+    <t>Kheybar Khorramabad</t>
+  </si>
+  <si>
+    <t>Al Orubah</t>
   </si>
   <si>
     <t>Al Wahda</t>
   </si>
   <si>
-    <t>Al Orubah</t>
-  </si>
-  <si>
     <t>Kristiansund</t>
   </si>
   <si>
-    <t>Kheybar Khorramabad</t>
+    <t>Levski Krumovgrad</t>
   </si>
   <si>
     <t>TB</t>
   </si>
   <si>
-    <t>Levski Krumovgrad</t>
+    <t>Al Jazeera</t>
   </si>
   <si>
     <t>Bani Yas</t>
   </si>
   <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>Zamalek</t>
   </si>
   <si>
@@ -565,33 +511,33 @@
     <t>['88']</t>
   </si>
   <si>
+    <t>['74']</t>
+  </si>
+  <si>
     <t>['40']</t>
   </si>
   <si>
-    <t>['74']</t>
-  </si>
-  <si>
     <t>['22', '51', '66', '90+2']</t>
   </si>
   <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['22', '79']</t>
+  </si>
+  <si>
+    <t>['30', '43']</t>
+  </si>
+  <si>
+    <t>['19', '80', '90+5']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
     <t>['81']</t>
   </si>
   <si>
-    <t>['30', '43']</t>
-  </si>
-  <si>
-    <t>['22', '79']</t>
-  </si>
-  <si>
-    <t>['27']</t>
-  </si>
-  <si>
-    <t>['36']</t>
-  </si>
-  <si>
-    <t>['19', '80', '90+5']</t>
-  </si>
-  <si>
     <t>['17', '82']</t>
   </si>
   <si>
@@ -607,24 +553,24 @@
     <t>['21']</t>
   </si>
   <si>
+    <t>['45', '45+5']</t>
+  </si>
+  <si>
     <t>['50']</t>
   </si>
   <si>
-    <t>['45', '45+5']</t>
-  </si>
-  <si>
     <t>['61']</t>
   </si>
   <si>
     <t>['10', '83', '19', '24', '35', '38', '65', '67', '75', '78']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
     <t>['69']</t>
   </si>
   <si>
-    <t>['76']</t>
-  </si>
-  <si>
     <t>['13', '87']</t>
   </si>
   <si>
@@ -655,12 +601,12 @@
     <t>['42', '55']</t>
   </si>
   <si>
+    <t>['47', '75']</t>
+  </si>
+  <si>
     <t>['15', '70', '86']</t>
   </si>
   <si>
-    <t>['47', '75']</t>
-  </si>
-  <si>
     <t>['69', '73', '78', '90+3']</t>
   </si>
   <si>
@@ -673,16 +619,16 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
     <t>['5', '44', '45+2']</t>
   </si>
   <si>
-    <t>['51']</t>
+    <t>['5', '58', '84', '89']</t>
   </si>
   <si>
     <t>['55', '75']</t>
-  </si>
-  <si>
-    <t>['5', '58', '84', '89']</t>
   </si>
   <si>
     <t>['90+9']</t>
@@ -1064,10 +1010,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD40"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1182,79 +1128,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45778</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -1269,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L2">
         <v>2.04</v>
@@ -1344,87 +1236,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="AK2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL2">
-        <v>1.32</v>
-      </c>
-      <c r="AM2">
-        <v>1.29</v>
-      </c>
-      <c r="AN2">
-        <v>1.68</v>
-      </c>
-      <c r="AO2">
-        <v>12</v>
-      </c>
-      <c r="AP2">
-        <v>1.24</v>
-      </c>
-      <c r="AQ2">
-        <v>1.47</v>
-      </c>
-      <c r="AR2">
-        <v>1.85</v>
-      </c>
-      <c r="AS2">
-        <v>2.32</v>
-      </c>
-      <c r="AT2">
-        <v>3.08</v>
-      </c>
-      <c r="AU2">
-        <v>3.34</v>
-      </c>
-      <c r="AV2">
-        <v>2.42</v>
-      </c>
-      <c r="AW2">
-        <v>1.85</v>
-      </c>
-      <c r="AX2">
-        <v>1.51</v>
-      </c>
-      <c r="AY2">
-        <v>1.28</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.67</v>
-      </c>
-      <c r="BC2">
-        <v>2.4</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>189</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45778.1875</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45778</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1439,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L3">
         <v>34</v>
@@ -1514,87 +1352,33 @@
         <v>1.55</v>
       </c>
       <c r="AJ3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AK3" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL3">
-        <v>9</v>
-      </c>
-      <c r="AM3">
-        <v>1.05</v>
-      </c>
-      <c r="AN3">
-        <v>1.01</v>
-      </c>
-      <c r="AO3">
-        <v>8</v>
-      </c>
-      <c r="AP3">
-        <v>1.24</v>
-      </c>
-      <c r="AQ3">
-        <v>1.51</v>
-      </c>
-      <c r="AR3">
-        <v>1.84</v>
-      </c>
-      <c r="AS3">
-        <v>2.29</v>
-      </c>
-      <c r="AT3">
-        <v>3.1</v>
-      </c>
-      <c r="AU3">
-        <v>3.5</v>
-      </c>
-      <c r="AV3">
-        <v>2.32</v>
-      </c>
-      <c r="AW3">
-        <v>1.82</v>
-      </c>
-      <c r="AX3">
-        <v>1.53</v>
-      </c>
-      <c r="AY3">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>8</v>
-      </c>
-      <c r="BC3">
-        <v>1.08</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>190</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45778.29166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45778</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1609,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L4">
         <v>3.03</v>
@@ -1684,87 +1468,33 @@
         <v>1.09</v>
       </c>
       <c r="AJ4" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL4">
-        <v>1.62</v>
-      </c>
-      <c r="AM4">
-        <v>1.25</v>
-      </c>
-      <c r="AN4">
-        <v>1.36</v>
-      </c>
-      <c r="AO4">
-        <v>10</v>
-      </c>
-      <c r="AP4">
-        <v>1.1</v>
-      </c>
-      <c r="AQ4">
-        <v>1.24</v>
-      </c>
-      <c r="AR4">
-        <v>1.45</v>
-      </c>
-      <c r="AS4">
-        <v>1.9</v>
-      </c>
-      <c r="AT4">
-        <v>2.23</v>
-      </c>
-      <c r="AU4">
-        <v>5.05</v>
-      </c>
-      <c r="AV4">
-        <v>3.34</v>
-      </c>
-      <c r="AW4">
-        <v>2.48</v>
-      </c>
-      <c r="AX4">
-        <v>1.8</v>
-      </c>
-      <c r="AY4">
-        <v>1.55</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.25</v>
-      </c>
-      <c r="BC4">
-        <v>1.73</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45778.3125</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45778</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1779,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L5">
         <v>2.25</v>
@@ -1854,87 +1584,33 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="AK5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>12</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.73</v>
-      </c>
-      <c r="BC5">
-        <v>2.4</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45778.3125</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45778</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1949,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L6">
         <v>1.96</v>
@@ -2024,87 +1700,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="AK6" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL6">
-        <v>1.28</v>
-      </c>
-      <c r="AM6">
-        <v>1.25</v>
-      </c>
-      <c r="AN6">
-        <v>1.77</v>
-      </c>
-      <c r="AO6">
-        <v>11</v>
-      </c>
-      <c r="AP6">
-        <v>1.21</v>
-      </c>
-      <c r="AQ6">
-        <v>1.41</v>
-      </c>
-      <c r="AR6">
-        <v>1.7</v>
-      </c>
-      <c r="AS6">
-        <v>2.05</v>
-      </c>
-      <c r="AT6">
-        <v>2.6</v>
-      </c>
-      <c r="AU6">
-        <v>3.75</v>
-      </c>
-      <c r="AV6">
-        <v>2.7</v>
-      </c>
-      <c r="AW6">
-        <v>2.05</v>
-      </c>
-      <c r="AX6">
-        <v>1.7</v>
-      </c>
-      <c r="AY6">
-        <v>1.44</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.57</v>
-      </c>
-      <c r="BC6">
-        <v>2.5</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>191</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45778.33333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45778</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -2119,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L7">
         <v>1.65</v>
@@ -2194,87 +1816,33 @@
         <v>1.22</v>
       </c>
       <c r="AJ7" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="AK7" t="s">
-        <v>210</v>
-      </c>
-      <c r="AL7">
-        <v>1.15</v>
-      </c>
-      <c r="AM7">
-        <v>1.18</v>
-      </c>
-      <c r="AN7">
-        <v>2.15</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7">
-        <v>1.42</v>
-      </c>
-      <c r="AR7">
-        <v>1.7</v>
-      </c>
-      <c r="AS7">
-        <v>2.05</v>
-      </c>
-      <c r="AT7">
-        <v>2.65</v>
-      </c>
-      <c r="AU7">
-        <v>3.65</v>
-      </c>
-      <c r="AV7">
-        <v>2.65</v>
-      </c>
-      <c r="AW7">
-        <v>2.05</v>
-      </c>
-      <c r="AX7">
-        <v>1.7</v>
-      </c>
-      <c r="AY7">
-        <v>1.42</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.44</v>
-      </c>
-      <c r="BC7">
-        <v>2.75</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>192</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45778.33333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45778</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2289,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L8">
         <v>2.68</v>
@@ -2364,120 +1932,66 @@
         <v>1.14</v>
       </c>
       <c r="AJ8" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="AK8" t="s">
-        <v>211</v>
-      </c>
-      <c r="AL8">
-        <v>1.52</v>
-      </c>
-      <c r="AM8">
-        <v>1.29</v>
-      </c>
-      <c r="AN8">
-        <v>1.44</v>
-      </c>
-      <c r="AO8">
-        <v>11</v>
-      </c>
-      <c r="AP8">
-        <v>1.24</v>
-      </c>
-      <c r="AQ8">
-        <v>1.47</v>
-      </c>
-      <c r="AR8">
-        <v>1.85</v>
-      </c>
-      <c r="AS8">
-        <v>2.34</v>
-      </c>
-      <c r="AT8">
-        <v>3.08</v>
-      </c>
-      <c r="AU8">
-        <v>3.34</v>
-      </c>
-      <c r="AV8">
-        <v>2.42</v>
-      </c>
-      <c r="AW8">
-        <v>1.85</v>
-      </c>
-      <c r="AX8">
-        <v>1.5</v>
-      </c>
-      <c r="AY8">
-        <v>1.28</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>2.1</v>
-      </c>
-      <c r="BC8">
-        <v>1.8</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>193</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45778.35416666666</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45778</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L9">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M9">
-        <v>3.76</v>
+        <v>6.6</v>
       </c>
       <c r="N9">
-        <v>2.75</v>
+        <v>11</v>
       </c>
       <c r="O9">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="R9">
         <v>1.22</v>
@@ -2486,168 +2000,114 @@
         <v>4</v>
       </c>
       <c r="T9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U9">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AA9">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB9">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC9">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE9">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AF9">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AI9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="AK9" t="s">
-        <v>212</v>
-      </c>
-      <c r="AL9">
-        <v>1.36</v>
-      </c>
-      <c r="AM9">
-        <v>1.22</v>
-      </c>
-      <c r="AN9">
-        <v>1.67</v>
-      </c>
-      <c r="AO9">
-        <v>11</v>
-      </c>
-      <c r="AP9">
-        <v>1.2</v>
-      </c>
-      <c r="AQ9">
-        <v>1.39</v>
-      </c>
-      <c r="AR9">
-        <v>1.64</v>
-      </c>
-      <c r="AS9">
-        <v>2</v>
-      </c>
-      <c r="AT9">
-        <v>2.52</v>
-      </c>
-      <c r="AU9">
-        <v>3.9</v>
-      </c>
-      <c r="AV9">
-        <v>2.78</v>
-      </c>
-      <c r="AW9">
-        <v>2.17</v>
-      </c>
-      <c r="AX9">
-        <v>1.73</v>
-      </c>
-      <c r="AY9">
-        <v>1.46</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.67</v>
-      </c>
-      <c r="BC9">
-        <v>2.1</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>181</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45778.35763888889</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45778</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L10">
-        <v>1.16</v>
+        <v>2.13</v>
       </c>
       <c r="M10">
-        <v>6.6</v>
+        <v>3.76</v>
       </c>
       <c r="N10">
-        <v>11</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="P10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q10">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
         <v>1.22</v>
@@ -2656,135 +2116,81 @@
         <v>4</v>
       </c>
       <c r="T10">
+        <v>2.1</v>
+      </c>
+      <c r="U10">
+        <v>1.67</v>
+      </c>
+      <c r="V10">
+        <v>4.5</v>
+      </c>
+      <c r="W10">
+        <v>1.18</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>17</v>
+      </c>
+      <c r="Z10">
+        <v>1.13</v>
+      </c>
+      <c r="AA10">
+        <v>5.25</v>
+      </c>
+      <c r="AB10">
+        <v>1.4</v>
+      </c>
+      <c r="AC10">
+        <v>2.73</v>
+      </c>
+      <c r="AD10">
         <v>2</v>
       </c>
-      <c r="U10">
-        <v>1.73</v>
-      </c>
-      <c r="V10">
-        <v>4.33</v>
-      </c>
-      <c r="W10">
-        <v>1.2</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>21</v>
-      </c>
-      <c r="Z10">
-        <v>1.12</v>
-      </c>
-      <c r="AA10">
-        <v>5.5</v>
-      </c>
-      <c r="AB10">
-        <v>1.37</v>
-      </c>
-      <c r="AC10">
-        <v>2.85</v>
-      </c>
-      <c r="AD10">
-        <v>1.92</v>
-      </c>
       <c r="AE10">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AF10">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AH10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AI10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AJ10" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="AK10" t="s">
-        <v>199</v>
-      </c>
-      <c r="AL10">
-        <v>1.05</v>
-      </c>
-      <c r="AM10">
-        <v>1.14</v>
-      </c>
-      <c r="AN10">
-        <v>3.9</v>
-      </c>
-      <c r="AO10">
-        <v>9</v>
-      </c>
-      <c r="AP10">
-        <v>1.16</v>
-      </c>
-      <c r="AQ10">
-        <v>1.3</v>
-      </c>
-      <c r="AR10">
-        <v>1.54</v>
-      </c>
-      <c r="AS10">
-        <v>1.85</v>
-      </c>
-      <c r="AT10">
-        <v>2.34</v>
-      </c>
-      <c r="AU10">
-        <v>4.35</v>
-      </c>
-      <c r="AV10">
-        <v>3.07</v>
-      </c>
-      <c r="AW10">
-        <v>2.33</v>
-      </c>
-      <c r="AX10">
-        <v>1.85</v>
-      </c>
-      <c r="AY10">
-        <v>1.56</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.18</v>
-      </c>
-      <c r="BC10">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>194</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45778.35763888889</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45778</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G11">
         <v>4</v>
@@ -2799,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L11">
         <v>1.7</v>
@@ -2874,132 +2280,78 @@
         <v>1.14</v>
       </c>
       <c r="AJ11" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="AK11" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL11">
-        <v>1.25</v>
-      </c>
-      <c r="AM11">
-        <v>1.21</v>
-      </c>
-      <c r="AN11">
-        <v>1.72</v>
-      </c>
-      <c r="AO11">
-        <v>22</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>1.22</v>
-      </c>
-      <c r="AR11">
-        <v>1.41</v>
-      </c>
-      <c r="AS11">
-        <v>1.71</v>
-      </c>
-      <c r="AT11">
-        <v>2.12</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>3.5</v>
-      </c>
-      <c r="AW11">
-        <v>2.52</v>
-      </c>
-      <c r="AX11">
-        <v>1.97</v>
-      </c>
-      <c r="AY11">
-        <v>1.58</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.44</v>
-      </c>
-      <c r="BC11">
-        <v>2.75</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45778.375</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45778</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L12">
-        <v>3.13</v>
+        <v>1.88</v>
       </c>
       <c r="M12">
-        <v>3.29</v>
+        <v>3.57</v>
       </c>
       <c r="N12">
-        <v>2.43</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="R12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S12">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -3020,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -3032,11 +2384,11 @@
         <v>0</v>
       </c>
       <c r="AF12">
+        <v>1.95</v>
+      </c>
+      <c r="AG12">
         <v>1.8</v>
       </c>
-      <c r="AG12">
-        <v>1.95</v>
-      </c>
       <c r="AH12">
         <v>0</v>
       </c>
@@ -3044,111 +2396,57 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="AK12" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2.3</v>
-      </c>
-      <c r="BC12">
-        <v>1.8</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>195</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45778</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>1</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L13">
         <v>1.67</v>
       </c>
       <c r="M13">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
         <v>1.44</v>
@@ -3157,25 +2455,25 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
+        <v>1.36</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <v>2.75</v>
+      </c>
+      <c r="U13">
         <v>1.4</v>
       </c>
-      <c r="S13">
-        <v>2.75</v>
-      </c>
-      <c r="T13">
-        <v>3</v>
-      </c>
-      <c r="U13">
-        <v>1.36</v>
-      </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>0</v>
@@ -3190,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC13">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -3202,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -3214,138 +2512,84 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="AK13" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>6</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.44</v>
-      </c>
-      <c r="BC13">
-        <v>3.25</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45778</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>157</v>
+      </c>
+      <c r="L14">
+        <v>3.13</v>
+      </c>
+      <c r="M14">
+        <v>3.29</v>
+      </c>
+      <c r="N14">
+        <v>2.43</v>
+      </c>
+      <c r="O14">
+        <v>2.3</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>1.8</v>
+      </c>
+      <c r="R14">
+        <v>1.4</v>
+      </c>
+      <c r="S14">
+        <v>2.75</v>
+      </c>
+      <c r="T14">
         <v>3</v>
       </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>175</v>
-      </c>
-      <c r="L14">
-        <v>2.05</v>
-      </c>
-      <c r="M14">
-        <v>3.27</v>
-      </c>
-      <c r="N14">
-        <v>4.2</v>
-      </c>
-      <c r="O14">
-        <v>1.67</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>2.75</v>
-      </c>
-      <c r="R14">
-        <v>1.5</v>
-      </c>
-      <c r="S14">
-        <v>2.5</v>
-      </c>
-      <c r="T14">
-        <v>3.5</v>
-      </c>
       <c r="U14">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>0</v>
@@ -3360,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC14">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3372,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -3384,138 +2628,84 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="AK14" t="s">
-        <v>213</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.67</v>
-      </c>
-      <c r="BC14">
-        <v>2.75</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45778</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
       <c r="K15" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L15">
+        <v>2.05</v>
+      </c>
+      <c r="M15">
+        <v>3.27</v>
+      </c>
+      <c r="N15">
+        <v>4.2</v>
+      </c>
+      <c r="O15">
         <v>1.67</v>
       </c>
-      <c r="M15">
-        <v>4</v>
-      </c>
-      <c r="N15">
-        <v>5.4</v>
-      </c>
-      <c r="O15">
-        <v>1.44</v>
-      </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R15">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>0</v>
@@ -3530,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC15">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -3542,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -3554,93 +2744,39 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="AK15" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>14</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.44</v>
-      </c>
-      <c r="BC15">
-        <v>3.1</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>196</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45778</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -3649,62 +2785,62 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L16">
+        <v>2.65</v>
+      </c>
+      <c r="M16">
+        <v>3.19</v>
+      </c>
+      <c r="N16">
+        <v>2.9</v>
+      </c>
+      <c r="O16">
+        <v>1.83</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>2.1</v>
+      </c>
+      <c r="R16">
+        <v>1.36</v>
+      </c>
+      <c r="S16">
+        <v>3</v>
+      </c>
+      <c r="T16">
+        <v>2.75</v>
+      </c>
+      <c r="U16">
+        <v>1.4</v>
+      </c>
+      <c r="V16">
+        <v>8</v>
+      </c>
+      <c r="W16">
+        <v>1.08</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>1.93</v>
+      </c>
+      <c r="AC16">
         <v>1.88</v>
       </c>
-      <c r="M16">
-        <v>3.57</v>
-      </c>
-      <c r="N16">
-        <v>4.5</v>
-      </c>
-      <c r="O16">
-        <v>1.57</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>2.75</v>
-      </c>
-      <c r="R16">
-        <v>1.44</v>
-      </c>
-      <c r="S16">
-        <v>2.63</v>
-      </c>
-      <c r="T16">
-        <v>3.25</v>
-      </c>
-      <c r="U16">
-        <v>1.33</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>1.07</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>2</v>
-      </c>
-      <c r="AC16">
-        <v>1.82</v>
-      </c>
       <c r="AD16">
         <v>0</v>
       </c>
@@ -3712,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -3724,87 +2860,33 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="AK16" t="s">
-        <v>214</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.57</v>
-      </c>
-      <c r="BC16">
-        <v>2.75</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45778</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -3819,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L17">
         <v>3.18</v>
@@ -3894,132 +2976,78 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="AK17" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>6</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>2.3</v>
-      </c>
-      <c r="BC17">
-        <v>1.8</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45778</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F18" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>157</v>
+      </c>
+      <c r="L18">
+        <v>1.67</v>
+      </c>
+      <c r="M18">
+        <v>3.85</v>
+      </c>
+      <c r="N18">
+        <v>5.7</v>
+      </c>
+      <c r="O18">
+        <v>1.44</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>3.25</v>
+      </c>
+      <c r="R18">
+        <v>1.4</v>
+      </c>
+      <c r="S18">
+        <v>2.75</v>
+      </c>
+      <c r="T18">
         <v>3</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18">
-        <v>2.65</v>
-      </c>
-      <c r="M18">
-        <v>3.19</v>
-      </c>
-      <c r="N18">
-        <v>2.9</v>
-      </c>
-      <c r="O18">
-        <v>1.83</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>2.1</v>
-      </c>
-      <c r="R18">
+      <c r="U18">
         <v>1.36</v>
-      </c>
-      <c r="S18">
-        <v>3</v>
-      </c>
-      <c r="T18">
-        <v>2.75</v>
-      </c>
-      <c r="U18">
-        <v>1.4</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -4040,10 +3068,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC18">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -4052,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -4064,87 +3092,33 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="AK18" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.83</v>
-      </c>
-      <c r="BC18">
-        <v>2.1</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45778.41666666666</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45778</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
         <v>96</v>
       </c>
-      <c r="E19" t="s">
-        <v>114</v>
-      </c>
       <c r="F19" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -4159,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L19">
         <v>2.31</v>
@@ -4234,87 +3208,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ19" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="AK19" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL19">
-        <v>1.31</v>
-      </c>
-      <c r="AM19">
-        <v>1.33</v>
-      </c>
-      <c r="AN19">
-        <v>1.53</v>
-      </c>
-      <c r="AO19">
-        <v>9</v>
-      </c>
-      <c r="AP19">
-        <v>1.25</v>
-      </c>
-      <c r="AQ19">
-        <v>1.52</v>
-      </c>
-      <c r="AR19">
-        <v>2.01</v>
-      </c>
-      <c r="AS19">
-        <v>2.24</v>
-      </c>
-      <c r="AT19">
-        <v>2.83</v>
-      </c>
-      <c r="AU19">
-        <v>3.84</v>
-      </c>
-      <c r="AV19">
-        <v>2.48</v>
-      </c>
-      <c r="AW19">
-        <v>1.96</v>
-      </c>
-      <c r="AX19">
-        <v>1.6</v>
-      </c>
-      <c r="AY19">
-        <v>1.37</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.8</v>
-      </c>
-      <c r="BC19">
-        <v>2.5</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>197</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45778.45833333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45778</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -4329,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L20">
         <v>2.5</v>
@@ -4404,87 +3324,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ20" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="AK20" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL20">
-        <v>1.36</v>
-      </c>
-      <c r="AM20">
-        <v>1.3</v>
-      </c>
-      <c r="AN20">
-        <v>1.44</v>
-      </c>
-      <c r="AO20">
-        <v>11</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>2.38</v>
-      </c>
-      <c r="BC20">
-        <v>1.8</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45778.45833333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45778</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -4499,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -4574,87 +3440,33 @@
         <v>1.28</v>
       </c>
       <c r="AJ21" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="AK21" t="s">
-        <v>216</v>
-      </c>
-      <c r="AL21">
-        <v>1.07</v>
-      </c>
-      <c r="AM21">
-        <v>1.14</v>
-      </c>
-      <c r="AN21">
-        <v>3.4</v>
-      </c>
-      <c r="AO21">
-        <v>12</v>
-      </c>
-      <c r="AP21">
-        <v>1.28</v>
-      </c>
-      <c r="AQ21">
-        <v>1.53</v>
-      </c>
-      <c r="AR21">
-        <v>1.91</v>
-      </c>
-      <c r="AS21">
-        <v>2.51</v>
-      </c>
-      <c r="AT21">
-        <v>3.34</v>
-      </c>
-      <c r="AU21">
-        <v>3.08</v>
-      </c>
-      <c r="AV21">
-        <v>2.28</v>
-      </c>
-      <c r="AW21">
-        <v>1.8</v>
-      </c>
-      <c r="AX21">
-        <v>1.44</v>
-      </c>
-      <c r="AY21">
-        <v>1.24</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.22</v>
-      </c>
-      <c r="BC21">
-        <v>4</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>198</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45778.46875</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45778</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F22" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -4669,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L22">
         <v>1.8</v>
@@ -4744,87 +3556,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ22" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AK22" t="s">
-        <v>217</v>
-      </c>
-      <c r="AL22">
-        <v>1.16</v>
-      </c>
-      <c r="AM22">
-        <v>1.24</v>
-      </c>
-      <c r="AN22">
-        <v>1.84</v>
-      </c>
-      <c r="AO22">
-        <v>15</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.53</v>
-      </c>
-      <c r="BC22">
-        <v>2.88</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>199</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45778.5</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45778</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4839,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L23">
         <v>2.91</v>
@@ -4914,257 +3672,149 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AK23" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>5</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>2.2</v>
-      </c>
-      <c r="BC23">
-        <v>1.91</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45778.51041666666</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45778</v>
       </c>
       <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
         <v>68</v>
       </c>
-      <c r="C24" t="s">
-        <v>86</v>
-      </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F24" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>157</v>
+      </c>
+      <c r="L24">
+        <v>4.1</v>
+      </c>
+      <c r="M24">
+        <v>2.65</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>2.5</v>
+      </c>
+      <c r="P24">
+        <v>5.25</v>
+      </c>
+      <c r="Q24">
+        <v>1.95</v>
+      </c>
+      <c r="R24">
+        <v>1.65</v>
+      </c>
+      <c r="S24">
+        <v>2.16</v>
+      </c>
+      <c r="T24">
+        <v>4.15</v>
+      </c>
+      <c r="U24">
+        <v>1.17</v>
+      </c>
+      <c r="V24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.15</v>
+      </c>
+      <c r="Y24">
+        <v>5</v>
+      </c>
+      <c r="Z24">
+        <v>1.67</v>
+      </c>
+      <c r="AA24">
+        <v>2.1</v>
+      </c>
+      <c r="AB24">
         <v>3</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>3</v>
-      </c>
-      <c r="K24" t="s">
-        <v>175</v>
-      </c>
-      <c r="L24">
-        <v>4.87</v>
-      </c>
-      <c r="M24">
-        <v>3.18</v>
-      </c>
-      <c r="N24">
-        <v>1.78</v>
-      </c>
-      <c r="O24">
-        <v>2.95</v>
-      </c>
-      <c r="P24">
-        <v>6.25</v>
-      </c>
-      <c r="Q24">
-        <v>1.67</v>
-      </c>
-      <c r="R24">
-        <v>1.52</v>
-      </c>
-      <c r="S24">
-        <v>2.3</v>
-      </c>
-      <c r="T24">
-        <v>3.65</v>
-      </c>
-      <c r="U24">
-        <v>1.22</v>
-      </c>
-      <c r="V24">
-        <v>8.1</v>
-      </c>
-      <c r="W24">
-        <v>1.04</v>
-      </c>
-      <c r="X24">
-        <v>1.11</v>
-      </c>
-      <c r="Y24">
-        <v>6</v>
-      </c>
-      <c r="Z24">
+      <c r="AC24">
+        <v>1.36</v>
+      </c>
+      <c r="AD24">
+        <v>6.5</v>
+      </c>
+      <c r="AE24">
+        <v>1.1</v>
+      </c>
+      <c r="AF24">
+        <v>2.38</v>
+      </c>
+      <c r="AG24">
         <v>1.53</v>
       </c>
-      <c r="AA24">
-        <v>2.38</v>
-      </c>
-      <c r="AB24">
-        <v>2.63</v>
-      </c>
-      <c r="AC24">
-        <v>1.44</v>
-      </c>
-      <c r="AD24">
-        <v>5.5</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
-      <c r="AF24">
-        <v>2.3</v>
-      </c>
-      <c r="AG24">
-        <v>1.57</v>
-      </c>
       <c r="AH24">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AK24" t="s">
-        <v>219</v>
-      </c>
-      <c r="AL24">
-        <v>1.36</v>
-      </c>
-      <c r="AM24">
-        <v>1.29</v>
-      </c>
-      <c r="AN24">
-        <v>1.18</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>2.95</v>
-      </c>
-      <c r="BC24">
-        <v>1.67</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>201</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45778.53125</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45778</v>
       </c>
       <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
         <v>68</v>
       </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5179,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L25">
         <v>1.53</v>
@@ -5254,427 +3904,265 @@
         <v>1.04</v>
       </c>
       <c r="AJ25" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AK25" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL25">
-        <v>1.3</v>
-      </c>
-      <c r="AM25">
-        <v>1.25</v>
-      </c>
-      <c r="AN25">
-        <v>2.3</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>1.37</v>
-      </c>
-      <c r="BC25">
-        <v>3.7</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45778.53125</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45778</v>
       </c>
       <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
         <v>68</v>
       </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L26">
-        <v>4.1</v>
+        <v>4.87</v>
       </c>
       <c r="M26">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="O26">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P26">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="Q26">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S26">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T26">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="U26">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V26">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB26">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AC26">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AD26">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG26">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH26">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AI26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ26" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="AK26" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL26">
-        <v>1.44</v>
-      </c>
-      <c r="AM26">
-        <v>1.38</v>
-      </c>
-      <c r="AN26">
-        <v>1.3</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2.5</v>
-      </c>
-      <c r="BC26">
-        <v>1.95</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>202</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45778.53125</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45778</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>157</v>
+      </c>
+      <c r="L27">
+        <v>2.5</v>
+      </c>
+      <c r="M27">
+        <v>2.52</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
         <v>2</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>175</v>
-      </c>
-      <c r="L27">
-        <v>1.85</v>
-      </c>
-      <c r="M27">
+      <c r="P27">
+        <v>4.33</v>
+      </c>
+      <c r="Q27">
+        <v>2.63</v>
+      </c>
+      <c r="R27">
+        <v>1.72</v>
+      </c>
+      <c r="S27">
+        <v>2.14</v>
+      </c>
+      <c r="T27">
         <v>3.8</v>
       </c>
-      <c r="N27">
-        <v>3.78</v>
-      </c>
-      <c r="O27">
-        <v>1.57</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>2.75</v>
-      </c>
-      <c r="R27">
-        <v>1.4</v>
-      </c>
-      <c r="S27">
-        <v>2.75</v>
-      </c>
-      <c r="T27">
-        <v>2.75</v>
-      </c>
       <c r="U27">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="V27">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="AC27">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AG27">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ27" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="AK27" t="s">
-        <v>221</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>0</v>
-      </c>
-      <c r="AO27">
-        <v>8</v>
-      </c>
-      <c r="AP27">
-        <v>0</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27">
-        <v>0</v>
-      </c>
-      <c r="AV27">
-        <v>0</v>
-      </c>
-      <c r="AW27">
-        <v>0</v>
-      </c>
-      <c r="AX27">
-        <v>0</v>
-      </c>
-      <c r="AY27">
-        <v>0</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.57</v>
-      </c>
-      <c r="BC27">
-        <v>2.75</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45778.54166666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45778</v>
       </c>
       <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
         <v>69</v>
       </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -5689,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L28">
         <v>1.89</v>
@@ -5764,93 +4252,39 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="AK28" t="s">
-        <v>222</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AO28">
-        <v>9</v>
-      </c>
-      <c r="AP28">
-        <v>0</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28">
-        <v>0</v>
-      </c>
-      <c r="AV28">
-        <v>0</v>
-      </c>
-      <c r="AW28">
-        <v>0</v>
-      </c>
-      <c r="AX28">
-        <v>0</v>
-      </c>
-      <c r="AY28">
-        <v>0</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.53</v>
-      </c>
-      <c r="BC28">
-        <v>2.75</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>203</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45778.54166666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45778</v>
       </c>
       <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
         <v>69</v>
       </c>
-      <c r="C29" t="s">
-        <v>88</v>
-      </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5859,168 +4293,114 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L29">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="N29">
-        <v>10</v>
+        <v>3.78</v>
       </c>
       <c r="O29">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="P29">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S29">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T29">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W29">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AC29">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AD29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH29">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="AK29" t="s">
-        <v>223</v>
-      </c>
-      <c r="AL29">
-        <v>1.06</v>
-      </c>
-      <c r="AM29">
-        <v>1.13</v>
-      </c>
-      <c r="AN29">
-        <v>3.75</v>
-      </c>
-      <c r="AO29">
-        <v>17</v>
-      </c>
-      <c r="AP29">
-        <v>1.1</v>
-      </c>
-      <c r="AQ29">
-        <v>1.25</v>
-      </c>
-      <c r="AR29">
-        <v>1.47</v>
-      </c>
-      <c r="AS29">
-        <v>1.8</v>
-      </c>
-      <c r="AT29">
-        <v>2.35</v>
-      </c>
-      <c r="AU29">
-        <v>5.05</v>
-      </c>
-      <c r="AV29">
-        <v>3.4</v>
-      </c>
-      <c r="AW29">
-        <v>2.4</v>
-      </c>
-      <c r="AX29">
-        <v>1.83</v>
-      </c>
-      <c r="AY29">
-        <v>1.49</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.25</v>
-      </c>
-      <c r="BC29">
-        <v>4</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>204</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45778.54166666666</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45778</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -6029,842 +4409,572 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L30">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="M30">
-        <v>2.52</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="P30">
-        <v>4.33</v>
+        <v>15.5</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R30">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="S30">
-        <v>2.14</v>
+        <v>3.75</v>
       </c>
       <c r="T30">
+        <v>2.2</v>
+      </c>
+      <c r="U30">
+        <v>1.62</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
+      </c>
+      <c r="W30">
+        <v>1.17</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>17</v>
+      </c>
+      <c r="Z30">
+        <v>1.14</v>
+      </c>
+      <c r="AA30">
+        <v>5.5</v>
+      </c>
+      <c r="AB30">
+        <v>1.47</v>
+      </c>
+      <c r="AC30">
+        <v>2.57</v>
+      </c>
+      <c r="AD30">
+        <v>2.2</v>
+      </c>
+      <c r="AE30">
+        <v>1.55</v>
+      </c>
+      <c r="AF30">
+        <v>1.8</v>
+      </c>
+      <c r="AG30">
+        <v>1.95</v>
+      </c>
+      <c r="AH30">
         <v>3.8</v>
       </c>
-      <c r="U30">
-        <v>1.16</v>
-      </c>
-      <c r="V30">
-        <v>9.4</v>
-      </c>
-      <c r="W30">
-        <v>1.03</v>
-      </c>
-      <c r="X30">
-        <v>1.17</v>
-      </c>
-      <c r="Y30">
-        <v>4.8</v>
-      </c>
-      <c r="Z30">
-        <v>1.75</v>
-      </c>
-      <c r="AA30">
-        <v>2</v>
-      </c>
-      <c r="AB30">
-        <v>3.25</v>
-      </c>
-      <c r="AC30">
-        <v>1.3</v>
-      </c>
-      <c r="AD30">
-        <v>7.5</v>
-      </c>
-      <c r="AE30">
-        <v>1.08</v>
-      </c>
-      <c r="AF30">
-        <v>2.4</v>
-      </c>
-      <c r="AG30">
-        <v>1.48</v>
-      </c>
-      <c r="AH30">
-        <v>19</v>
-      </c>
       <c r="AI30">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AJ30" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AK30" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL30">
-        <v>1.44</v>
-      </c>
-      <c r="AM30">
-        <v>1.5</v>
-      </c>
-      <c r="AN30">
-        <v>1.5</v>
-      </c>
-      <c r="AO30">
-        <v>2</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30">
-        <v>0</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
-      <c r="AW30">
-        <v>0</v>
-      </c>
-      <c r="AX30">
-        <v>0</v>
-      </c>
-      <c r="AY30">
-        <v>0</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>2</v>
-      </c>
-      <c r="BC30">
-        <v>2.63</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>205</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45778.54166666666</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45778</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L31">
+        <v>2.3</v>
+      </c>
+      <c r="M31">
+        <v>2.9</v>
+      </c>
+      <c r="N31">
+        <v>3.08</v>
+      </c>
+      <c r="O31">
+        <v>2.25</v>
+      </c>
+      <c r="P31">
+        <v>7.5</v>
+      </c>
+      <c r="Q31">
+        <v>1.91</v>
+      </c>
+      <c r="R31">
+        <v>1.48</v>
+      </c>
+      <c r="S31">
+        <v>2.55</v>
+      </c>
+      <c r="T31">
+        <v>3.28</v>
+      </c>
+      <c r="U31">
+        <v>1.32</v>
+      </c>
+      <c r="V31">
+        <v>6.7</v>
+      </c>
+      <c r="W31">
+        <v>1.06</v>
+      </c>
+      <c r="X31">
         <v>1.02</v>
       </c>
-      <c r="M31">
-        <v>13</v>
-      </c>
-      <c r="N31">
-        <v>56</v>
-      </c>
-      <c r="O31">
-        <v>1.07</v>
-      </c>
-      <c r="P31">
-        <v>21</v>
-      </c>
-      <c r="Q31">
-        <v>9</v>
-      </c>
-      <c r="R31">
-        <v>1.18</v>
-      </c>
-      <c r="S31">
-        <v>3.8</v>
-      </c>
-      <c r="T31">
-        <v>1.8</v>
-      </c>
-      <c r="U31">
-        <v>1.67</v>
-      </c>
-      <c r="V31">
-        <v>4.33</v>
-      </c>
-      <c r="W31">
-        <v>1.18</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
       <c r="Y31">
-        <v>29</v>
+        <v>7.5</v>
       </c>
       <c r="Z31">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AA31">
-        <v>5.5</v>
+        <v>2.67</v>
       </c>
       <c r="AB31">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AC31">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD31">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="AE31">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="AG31">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AH31">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
       <c r="AI31">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AJ31" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="AK31" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL31">
-        <v>1.01</v>
-      </c>
-      <c r="AM31">
-        <v>1.04</v>
-      </c>
-      <c r="AN31">
-        <v>8</v>
-      </c>
-      <c r="AO31">
-        <v>10</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.07</v>
-      </c>
-      <c r="BC31">
-        <v>9</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>206</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45778.5625</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45778</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L32">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="M32">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="N32">
-        <v>3.08</v>
+        <v>56</v>
       </c>
       <c r="O32">
-        <v>2.25</v>
+        <v>1.07</v>
       </c>
       <c r="P32">
-        <v>7.5</v>
+        <v>21</v>
       </c>
       <c r="Q32">
-        <v>1.91</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="S32">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="T32">
-        <v>3.28</v>
+        <v>1.8</v>
       </c>
       <c r="U32">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V32">
-        <v>6.7</v>
+        <v>4.33</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>7.5</v>
+        <v>29</v>
       </c>
       <c r="Z32">
+        <v>1.11</v>
+      </c>
+      <c r="AA32">
+        <v>5.5</v>
+      </c>
+      <c r="AB32">
+        <v>1.42</v>
+      </c>
+      <c r="AC32">
+        <v>2.62</v>
+      </c>
+      <c r="AD32">
+        <v>1.7</v>
+      </c>
+      <c r="AE32">
+        <v>1.95</v>
+      </c>
+      <c r="AF32">
+        <v>2.4</v>
+      </c>
+      <c r="AG32">
+        <v>1.5</v>
+      </c>
+      <c r="AH32">
+        <v>2.7</v>
+      </c>
+      <c r="AI32">
         <v>1.4</v>
-      </c>
-      <c r="AA32">
-        <v>2.67</v>
-      </c>
-      <c r="AB32">
-        <v>2.3</v>
-      </c>
-      <c r="AC32">
-        <v>1.57</v>
-      </c>
-      <c r="AD32">
-        <v>3.9</v>
-      </c>
-      <c r="AE32">
-        <v>1.2</v>
-      </c>
-      <c r="AF32">
-        <v>1.94</v>
-      </c>
-      <c r="AG32">
-        <v>1.77</v>
-      </c>
-      <c r="AH32">
-        <v>9.5</v>
-      </c>
-      <c r="AI32">
-        <v>1.06</v>
       </c>
       <c r="AJ32" t="s">
         <v>182</v>
       </c>
       <c r="AK32" t="s">
-        <v>224</v>
-      </c>
-      <c r="AL32">
-        <v>1.36</v>
-      </c>
-      <c r="AM32">
-        <v>1.32</v>
-      </c>
-      <c r="AN32">
-        <v>1.53</v>
-      </c>
-      <c r="AO32">
-        <v>9</v>
-      </c>
-      <c r="AP32">
-        <v>1.42</v>
-      </c>
-      <c r="AQ32">
-        <v>1.73</v>
-      </c>
-      <c r="AR32">
-        <v>2.52</v>
-      </c>
-      <c r="AS32">
-        <v>2.78</v>
-      </c>
-      <c r="AT32">
-        <v>3.75</v>
-      </c>
-      <c r="AU32">
-        <v>2.63</v>
-      </c>
-      <c r="AV32">
-        <v>2.04</v>
-      </c>
-      <c r="AW32">
-        <v>1.64</v>
-      </c>
-      <c r="AX32">
-        <v>1.39</v>
-      </c>
-      <c r="AY32">
-        <v>1.21</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>2.25</v>
-      </c>
-      <c r="BC32">
-        <v>1.91</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45778.5625</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45778</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>157</v>
+      </c>
+      <c r="L33">
+        <v>4.6</v>
+      </c>
+      <c r="M33">
+        <v>3.8</v>
+      </c>
+      <c r="N33">
+        <v>1.63</v>
+      </c>
+      <c r="O33">
+        <v>2.75</v>
+      </c>
+      <c r="P33">
+        <v>8.5</v>
+      </c>
+      <c r="Q33">
+        <v>1.53</v>
+      </c>
+      <c r="R33">
+        <v>1.32</v>
+      </c>
+      <c r="S33">
+        <v>2.99</v>
+      </c>
+      <c r="T33">
+        <v>2.45</v>
+      </c>
+      <c r="U33">
+        <v>1.48</v>
+      </c>
+      <c r="V33">
+        <v>5.8</v>
+      </c>
+      <c r="W33">
+        <v>1.1</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>11.4</v>
+      </c>
+      <c r="Z33">
+        <v>1.21</v>
+      </c>
+      <c r="AA33">
+        <v>3.74</v>
+      </c>
+      <c r="AB33">
+        <v>1.73</v>
+      </c>
+      <c r="AC33">
         <v>2</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>2</v>
-      </c>
-      <c r="K33" t="s">
-        <v>175</v>
-      </c>
-      <c r="L33">
-        <v>1.29</v>
-      </c>
-      <c r="M33">
-        <v>5.25</v>
-      </c>
-      <c r="N33">
-        <v>9</v>
-      </c>
-      <c r="O33">
-        <v>1.25</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>4</v>
-      </c>
-      <c r="R33">
-        <v>1.3</v>
-      </c>
-      <c r="S33">
-        <v>3.4</v>
-      </c>
-      <c r="T33">
-        <v>2.5</v>
-      </c>
-      <c r="U33">
-        <v>1.5</v>
-      </c>
-      <c r="V33">
-        <v>5.5</v>
-      </c>
-      <c r="W33">
-        <v>1.13</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>1.6</v>
-      </c>
-      <c r="AC33">
+      <c r="AD33">
+        <v>2.65</v>
+      </c>
+      <c r="AE33">
+        <v>1.42</v>
+      </c>
+      <c r="AF33">
+        <v>1.62</v>
+      </c>
+      <c r="AG33">
         <v>2.1</v>
       </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>2</v>
-      </c>
-      <c r="AG33">
-        <v>1.73</v>
-      </c>
       <c r="AH33">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ33" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="AK33" t="s">
-        <v>225</v>
-      </c>
-      <c r="AL33">
-        <v>1.14</v>
-      </c>
-      <c r="AM33">
-        <v>1.23</v>
-      </c>
-      <c r="AN33">
-        <v>2.43</v>
-      </c>
-      <c r="AO33">
-        <v>16</v>
-      </c>
-      <c r="AP33">
-        <v>0</v>
-      </c>
-      <c r="AQ33">
-        <v>1.65</v>
-      </c>
-      <c r="AR33">
-        <v>2.09</v>
-      </c>
-      <c r="AS33">
-        <v>2.53</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33">
-        <v>0</v>
-      </c>
-      <c r="AV33">
-        <v>2.11</v>
-      </c>
-      <c r="AW33">
-        <v>1.66</v>
-      </c>
-      <c r="AX33">
-        <v>1.44</v>
-      </c>
-      <c r="AY33">
-        <v>0</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.25</v>
-      </c>
-      <c r="BC33">
-        <v>4</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>164</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45778.57291666666</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45778</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L34">
-        <v>4.6</v>
+        <v>1.29</v>
       </c>
       <c r="M34">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="N34">
-        <v>1.63</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="P34">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="R34">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S34">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="T34">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U34">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V34">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB34">
+        <v>1.6</v>
+      </c>
+      <c r="AC34">
+        <v>2.1</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>2</v>
+      </c>
+      <c r="AG34">
         <v>1.73</v>
       </c>
-      <c r="AC34">
-        <v>2</v>
-      </c>
-      <c r="AD34">
-        <v>2.65</v>
-      </c>
-      <c r="AE34">
-        <v>1.42</v>
-      </c>
-      <c r="AF34">
-        <v>1.62</v>
-      </c>
-      <c r="AG34">
-        <v>2.1</v>
-      </c>
       <c r="AH34">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="AK34" t="s">
-        <v>182</v>
-      </c>
-      <c r="AL34">
-        <v>2.02</v>
-      </c>
-      <c r="AM34">
-        <v>1.25</v>
-      </c>
-      <c r="AN34">
-        <v>1.12</v>
-      </c>
-      <c r="AO34">
-        <v>8</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>2.75</v>
-      </c>
-      <c r="BC34">
-        <v>1.53</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>207</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45778.57291666666</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45778</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -6879,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L35">
         <v>3.28</v>
@@ -6954,87 +5064,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ35" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AK35" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL35">
-        <v>1.37</v>
-      </c>
-      <c r="AM35">
-        <v>1.35</v>
-      </c>
-      <c r="AN35">
-        <v>1.2</v>
-      </c>
-      <c r="AO35">
-        <v>10</v>
-      </c>
-      <c r="AP35">
-        <v>1.38</v>
-      </c>
-      <c r="AQ35">
-        <v>1.65</v>
-      </c>
-      <c r="AR35">
-        <v>2.07</v>
-      </c>
-      <c r="AS35">
-        <v>2.49</v>
-      </c>
-      <c r="AT35">
-        <v>3.45</v>
-      </c>
-      <c r="AU35">
-        <v>2.82</v>
-      </c>
-      <c r="AV35">
-        <v>2.16</v>
-      </c>
-      <c r="AW35">
-        <v>1.7</v>
-      </c>
-      <c r="AX35">
-        <v>1.44</v>
-      </c>
-      <c r="AY35">
-        <v>1.21</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>2.3</v>
-      </c>
-      <c r="BC35">
-        <v>1.9</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45778.58333333334</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45778</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F36" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -7049,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L36">
         <v>1.59</v>
@@ -7124,87 +5180,33 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="AK36" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
-        <v>0</v>
-      </c>
-      <c r="AO36">
-        <v>11</v>
-      </c>
-      <c r="AP36">
-        <v>0</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>0</v>
-      </c>
-      <c r="AV36">
-        <v>0</v>
-      </c>
-      <c r="AW36">
-        <v>0</v>
-      </c>
-      <c r="AX36">
-        <v>0</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>1.4</v>
-      </c>
-      <c r="BC36">
-        <v>3.1</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45778.60416666666</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45778</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -7219,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L37">
         <v>3.04</v>
@@ -7294,87 +5296,33 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="AK37" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
-      </c>
-      <c r="AO37">
-        <v>17</v>
-      </c>
-      <c r="AP37">
-        <v>0</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37">
-        <v>0</v>
-      </c>
-      <c r="AV37">
-        <v>0</v>
-      </c>
-      <c r="AW37">
-        <v>0</v>
-      </c>
-      <c r="AX37">
-        <v>0</v>
-      </c>
-      <c r="AY37">
-        <v>0</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>2.2</v>
-      </c>
-      <c r="BC37">
-        <v>1.67</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45778.625</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45778</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7389,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L38">
         <v>2.25</v>
@@ -7464,87 +5412,33 @@
         <v>1.14</v>
       </c>
       <c r="AJ38" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AK38" t="s">
-        <v>227</v>
-      </c>
-      <c r="AL38">
-        <v>1.32</v>
-      </c>
-      <c r="AM38">
-        <v>1.29</v>
-      </c>
-      <c r="AN38">
-        <v>1.7</v>
-      </c>
-      <c r="AO38">
-        <v>9</v>
-      </c>
-      <c r="AP38">
-        <v>1.13</v>
-      </c>
-      <c r="AQ38">
-        <v>1.26</v>
-      </c>
-      <c r="AR38">
-        <v>1.47</v>
-      </c>
-      <c r="AS38">
-        <v>1.8</v>
-      </c>
-      <c r="AT38">
-        <v>2.35</v>
-      </c>
-      <c r="AU38">
-        <v>5.25</v>
-      </c>
-      <c r="AV38">
-        <v>3.5</v>
-      </c>
-      <c r="AW38">
-        <v>2.5</v>
-      </c>
-      <c r="AX38">
-        <v>1.88</v>
-      </c>
-      <c r="AY38">
-        <v>1.52</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.67</v>
-      </c>
-      <c r="BC38">
-        <v>2.3</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>209</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45778.64583333334</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45778</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -7559,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L39">
         <v>1.86</v>
@@ -7634,87 +5528,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ39" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="AK39" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL39">
-        <v>1.36</v>
-      </c>
-      <c r="AM39">
-        <v>1.28</v>
-      </c>
-      <c r="AN39">
-        <v>1.75</v>
-      </c>
-      <c r="AO39">
-        <v>10</v>
-      </c>
-      <c r="AP39">
-        <v>0</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39">
-        <v>0</v>
-      </c>
-      <c r="AV39">
-        <v>0</v>
-      </c>
-      <c r="AW39">
-        <v>0</v>
-      </c>
-      <c r="AX39">
-        <v>0</v>
-      </c>
-      <c r="AY39">
-        <v>0</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.5</v>
-      </c>
-      <c r="BC39">
-        <v>3.4</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>210</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45778.66666666666</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45778</v>
       </c>
       <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
         <v>77</v>
       </c>
-      <c r="C40" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" t="s">
-        <v>95</v>
-      </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -7729,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="L40">
         <v>1.31</v>
@@ -7804,66 +5644,12 @@
         <v>1.17</v>
       </c>
       <c r="AJ40" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="AK40" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL40">
-        <v>1.17</v>
-      </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>2.6</v>
-      </c>
-      <c r="AO40">
-        <v>11</v>
-      </c>
-      <c r="AP40">
-        <v>1.25</v>
-      </c>
-      <c r="AQ40">
-        <v>1.43</v>
-      </c>
-      <c r="AR40">
-        <v>1.99</v>
-      </c>
-      <c r="AS40">
-        <v>2.38</v>
-      </c>
-      <c r="AT40">
-        <v>3.2</v>
-      </c>
-      <c r="AU40">
-        <v>3.28</v>
-      </c>
-      <c r="AV40">
-        <v>2.33</v>
-      </c>
-      <c r="AW40">
-        <v>1.81</v>
-      </c>
-      <c r="AX40">
-        <v>1.46</v>
-      </c>
-      <c r="AY40">
-        <v>1.26</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>1.25</v>
-      </c>
-      <c r="BC40">
-        <v>4.33</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45778.875</v>
       </c>
     </row>

--- a/jogos_2025-05-01.xlsx
+++ b/jogos_2025-05-01.xlsx
@@ -762,119 +762,119 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>6.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.22</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.13</v>
-      </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.05</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['60', '88']</t>
+          <t>['9', '36', '57', '74', '77']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45778.29166666666</v>
@@ -891,119 +891,119 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="T4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
         <v>10</v>
       </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['60', '88']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.01</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['9', '36', '57', '74', '77']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AI4" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45778.29166666666</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.39</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.39</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.5</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['9', '24', '45+2', '64']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['13', '47']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.44</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['63', '89']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45778.33333333334</v>
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['63', '89']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['9', '24', '45+2', '64']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['13', '47']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45778.33333333334</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.13</v>
+        <v>1.16</v>
       </c>
       <c r="M10" t="n">
-        <v>3.76</v>
+        <v>6.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -1725,59 +1725,59 @@
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['42', '55']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45778.35763888889</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.16</v>
+        <v>2.13</v>
       </c>
       <c r="M11" t="n">
-        <v>6.6</v>
+        <v>3.76</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
         <v>1.22</v>
@@ -1854,59 +1854,59 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['42', '55']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45778.35763888889</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['30', '43']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['15', '70', '86']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.67</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="AJ13" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45778.41666666666</v>
@@ -2191,16 +2191,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.18</v>
+        <v>2.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['19', '80', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45778.41666666666</v>
@@ -2320,60 +2320,60 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.75</v>
       </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2397,19 +2397,19 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['30', '43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['15', '70', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45778.41666666666</v>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['47', '75']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['22', '79']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45778.41666666666</v>
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2655,14 +2655,14 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['19', '80', '90+5']</t>
+          <t>['22', '79']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45778.41666666666</v>
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>3.18</v>
       </c>
       <c r="M18" t="n">
-        <v>3.57</v>
+        <v>3.32</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>2.39</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2784,32 +2784,32 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['47', '75']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45778.41666666666</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.13</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.29</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.43</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.4</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2913,21 +2913,21 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45778.41666666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.53</v>
+        <v>4.87</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N25" t="n">
-        <v>6.79</v>
+        <v>1.78</v>
       </c>
       <c r="O25" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
         <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
         <v>3.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
         <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3699,20 +3699,20 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '44', '45+2']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.37</v>
+        <v>2.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45778.53125</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>6.79</v>
       </c>
       <c r="O26" t="n">
-        <v>5.1</v>
+        <v>2.12</v>
       </c>
       <c r="P26" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.84</v>
+        <v>8.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="S26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45778.53125</v>
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y27" t="n">
         <v>3</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.53</v>
       </c>
-      <c r="X27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['5', '44', '45+2']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45778.53125</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="M28" t="n">
-        <v>2.52</v>
+        <v>3.59</v>
       </c>
       <c r="N28" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
         <v>3</v>
       </c>
-      <c r="O28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.14</v>
-      </c>
       <c r="T28" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA28" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '45+5']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '58', '84', '89']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45778.54166666666</v>
@@ -4116,35 +4116,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.59</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>5.38</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC29" t="n">
         <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['45', '45+5']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['5', '58', '84', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45778.54166666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="Y30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['55', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45778.54166666666</v>
@@ -4374,32 +4374,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="O31" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.38</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="Z31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['55', '75']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA31" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45778.54166666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,109 +4900,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Aqaba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N35" t="n">
-        <v>9</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>7</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['35', '38']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.14</v>
+        <v>2.02</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.43</v>
+        <v>1.12</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45778.57291666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aqaba</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.6</v>
+        <v>1.29</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="N36" t="n">
-        <v>1.63</v>
+        <v>9</v>
       </c>
       <c r="O36" t="n">
-        <v>5.21</v>
+        <v>1.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['35', '38']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>2.02</v>
+        <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.12</v>
+        <v>2.43</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45778.57291666666</v>
